--- a/pcaf work.xlsx
+++ b/pcaf work.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\pcaf-wireframe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325FFB99-9FDA-49B3-8DCD-67D2B64776C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89C47153-B5EC-4248-AC77-333FE8751F15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -890,7 +890,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -925,6 +925,18 @@
     <font>
       <u/>
       <sz val="11"/>
+      <name val="Rockwell"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Rockwell"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFFF0000"/>
       <name val="Rockwell"/>
       <family val="1"/>
     </font>
@@ -971,7 +983,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -990,6 +1002,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2882,31 +2903,31 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="3" t="s">
+      <c r="A56" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C56" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="G56" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H56" s="5" t="s">
+      <c r="G56" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="I56" s="3" t="s">
+      <c r="I56" s="7" t="s">
         <v>204</v>
       </c>
     </row>
